--- a/EndResult/50m Rygg.xlsx
+++ b/EndResult/50m Rygg.xlsx
@@ -476,20 +476,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27,18</t>
+          <t>27,08</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>02.12.2024</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Reykjavík</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -576,25 +576,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Christoffer Tofte Haarsaker</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28,07</t>
+          <t>28,06</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.01.2015</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -611,25 +611,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fredrik Tronvoll</t>
+          <t>Christoffer Tofte Haarsaker</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28,18</t>
+          <t>28,07</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28.10.2012</t>
+          <t>16.01.2015</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,25 +646,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emil Vindvik</t>
+          <t>Fredrik Tronvoll</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28,23</t>
+          <t>28,18</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.09.2024</t>
+          <t>28.10.2012</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -681,25 +681,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Albert Barrabino</t>
+          <t>Emil Vindvik</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,31</t>
+          <t>28,23</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>14.09.2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bodø</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -751,25 +751,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Michael Alexander Calder</t>
+          <t>Albert Barrabino</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,55</t>
+          <t>28,31</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>04.03.2005</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -786,25 +786,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Per Osland</t>
+          <t>Michael Alexander Calder</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28,60</t>
+          <t>28,55</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>04.03.2005</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1278,20 +1278,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28,69</t>
+          <t>27,83</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>681</v>
+        <v>745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14.11.2024</t>
+          <t>13.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bodø</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/EndResult/50m Rygg.xlsx
+++ b/EndResult/50m Rygg.xlsx
@@ -716,7 +716,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anders Kristensen</t>
+          <t>Albert Barrabino</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.11.2006</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Albert Barrabino</t>
+          <t>Anders Kristensen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>10.11.2006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1047,25 +1047,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Simon Moe</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,49</t>
+          <t>30,45</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>02.07.2016</t>
+          <t>04.07.2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1082,25 +1082,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bergman Olof Andreas</t>
+          <t>Simon Moe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30,56</t>
+          <t>30,49</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29.04.2018</t>
+          <t>02.07.2016</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1117,25 +1117,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Bergman Olof Andreas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,69</t>
+          <t>30,56</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.04.2024</t>
+          <t>29.04.2018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1152,25 +1152,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gleb Eriksson</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30,77</t>
+          <t>30,69</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>09.07.2005</t>
+          <t>13.04.2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1187,25 +1187,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Gleb Eriksson</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31,20</t>
+          <t>30,77</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.02.2015</t>
+          <t>09.07.2005</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1448,12 +1448,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sara Juul Wolfgang</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,82</t>
+          <t>31,83</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.10.2015</t>
+          <t>19.01.2018</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Sara Juul Wolfgang</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31,83</t>
+          <t>31,82</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19.01.2018</t>
+          <t>18.10.2015</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1679,20 +1679,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29,87</t>
+          <t>28,84</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>727</v>
+        <v>807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>03.07.2025</t>
+          <t>17.04.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rud</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
